--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Opti-Grow\Opti-Grow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{537EDCAC-39F7-431F-90B9-BACA903EA2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9C7679-4ABB-4707-A40B-0FE9CDA2DD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9DCC0264-F1BD-4C6D-866F-42986DE1B9CB}"/>
   </bookViews>
